--- a/outputs/comercial/auditoria/Win_Back.xlsx
+++ b/outputs/comercial/auditoria/Win_Back.xlsx
@@ -563,7 +563,7 @@
         <v>46030</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -602,7 +602,7 @@
         <v>45911</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>46100</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
         <v>46090</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
         <v>46076</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>46042</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>46050</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         <v>46033</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
         <v>46089</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>46080</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45921</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>46081</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>45966</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>45932</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>46048</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         <v>45959</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -1187,7 +1187,7 @@
         <v>45996</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>46030</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>45932</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>45980</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>46003</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>46016</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>45917</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>46034</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>45977</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>45992</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>45994</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>45903</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>45906</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>45857</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>45837</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>46004</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1811,7 +1811,7 @@
         <v>45991</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>45970</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>45992</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>45987</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>46068</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>45910</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>45876</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>46081</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>46005</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>45998</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>45990</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>46064</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
         <v>45897</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         <v>46081</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>46019</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>46130</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
